--- a/public/boq/interior-boq-template.xlsx
+++ b/public/boq/interior-boq-template.xlsx
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fill the [brackets], quantities and rates. From the item library at ahromlabs.com/boq/items; check a filled BOQ at ahromlabs.com/boq/check.</t>
+          <t>Fill the [brackets], quantities and rates. From the item library at ahromlabs.com/boq/items (free under CC BY 4.0, credit Ahrom Labs); check a filled BOQ at ahromlabs.com/boq/check.</t>
         </is>
       </c>
     </row>
